--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="106">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T16:11:49+00:00</t>
+    <t>2025-08-01T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,7 +237,10 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: null</t>
+    <t>Mapping: AuthorDocumentEntryCDA</t>
+  </si>
+  <si>
+    <t>Mapping: AuthorDocumentEntryDICOMKOS</t>
   </si>
   <si>
     <t/>
@@ -298,7 +301,7 @@
 </t>
   </si>
   <si>
-    <t>ette métadonnée représente le rôle joué par l’auteur vis-à-vis du patient lors de la constitution du lot de soumission, c'est-à-dire à quel titre l’auteur est intervenu vis-à-vis du patient (ex : médecin traitant, Responsable de l'admission, Membre de l'équipe de soins, etc.).</t>
+    <t>cette métadonnée représente le rôle joué par l’auteur vis-à-vis du patient lors de la constitution du lot de soumission, c'est-à-dire à quel titre l’auteur est intervenu vis-à-vis du patient (ex : médecin traitant, Responsable de l'admission, Membre de l'équipe de soins, etc.).</t>
   </si>
   <si>
     <t>**Author Role**</t>
@@ -677,7 +680,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.83984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="33.33984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="146.93359375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -794,7 +797,7 @@
         <v>72</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
@@ -806,26 +809,26 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -836,491 +839,491 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y5" s="2"/>
       <c r="Z5" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T13:09:58+00:00</t>
+    <t>2025-08-04T10:11:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T10:11:31+00:00</t>
+    <t>2025-08-04T13:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T13:10:17+00:00</t>
+    <t>2026-06-10T15:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/Author</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdsm4dmp/StructureDefinition/Author|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -310,7 +310,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J47-FunctionCode-CISIS/FHIR/JDV-J47-FunctionCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J47-FunctionCode-CISIS/FHIR/JDV-J47-FunctionCode-CISIS|20250523120000</t>
   </si>
   <si>
     <t>Author.role</t>
@@ -331,7 +331,7 @@
     <t>**AutorSpecialty**</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J01-XdsAuthorSpecialty-CISIS/FHIR/JDV-J01-XdsAuthorSpecialty-CISIS|20260505120000</t>
   </si>
   <si>
     <t>Author.specialty</t>
@@ -670,7 +670,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="83.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="98.328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:39:40+00:00</t>
+    <t>2026-06-10T15:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:45:32+00:00</t>
+    <t>2026-06-10T15:59:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T15:59:45+00:00</t>
+    <t>2026-06-10T16:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:12:06+00:00</t>
+    <t>2026-06-10T16:18:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:18:52+00:00</t>
+    <t>2026-06-11T15:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:47:13+00:00</t>
+    <t>2026-06-11T15:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T15:59:09+00:00</t>
+    <t>2026-06-11T16:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:49:00+00:00</t>
+    <t>2026-06-12T14:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:52:39+00:00</t>
+    <t>2026-06-12T14:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:55:33+00:00</t>
+    <t>2026-06-12T14:56:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:56:09+00:00</t>
+    <t>2026-06-12T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:58:42+00:00</t>
+    <t>2026-06-12T15:04:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:04:49+00:00</t>
+    <t>2026-06-12T15:09:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:09:19+00:00</t>
+    <t>2026-06-12T15:31:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:31:20+00:00</t>
+    <t>2026-06-12T15:45:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:45:22+00:00</t>
+    <t>2026-06-12T16:24:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T16:24:39+00:00</t>
+    <t>2026-06-16T12:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:17:15+00:00</t>
+    <t>2026-06-16T12:25:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:25:33+00:00</t>
+    <t>2026-06-17T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:47:53+00:00</t>
+    <t>2026-06-17T07:58:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T07:58:49+00:00</t>
+    <t>2026-06-17T08:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:05:28+00:00</t>
+    <t>2026-06-17T08:38:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:38:09+00:00</t>
+    <t>2026-06-17T08:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:46:38+00:00</t>
+    <t>2026-06-17T08:50:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:50:19+00:00</t>
+    <t>2026-06-17T11:32:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:32:53+00:00</t>
+    <t>2026-06-17T11:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:35:28+00:00</t>
+    <t>2026-06-17T11:36:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
+++ b/add-info-dmp/ig/StructureDefinition-AuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T11:36:10+00:00</t>
+    <t>2026-06-17T12:12:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
